--- a/artfynd/S 485-2024 artfynd.xlsx
+++ b/artfynd/S 485-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108664149</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>PÖN0096a Grums Spelflyktsinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045946</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994398</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994405</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96316969</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994397</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1413,6 +1448,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994399</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1515,6 +1555,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994403</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994404</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1719,6 +1769,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994406</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1821,6 +1876,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994410</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1923,6 +1983,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994534</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2025,6 +2090,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994537</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2127,6 +2197,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994547</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2229,6 +2304,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994548</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2331,6 +2411,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994549</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2433,6 +2518,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994551</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2535,6 +2625,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994552</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2637,6 +2732,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994553</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2739,6 +2839,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994554</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2841,6 +2946,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994538</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2943,6 +3053,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994536</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3058,6 +3173,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115462923</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3185,6 +3305,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108673787</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3306,6 +3431,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108675002</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3414,6 +3544,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108971712</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3522,6 +3657,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108971713</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3630,6 +3770,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108971714</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3742,6 +3887,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115929069</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3868,6 +4018,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116255184</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3999,6 +4154,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122965599</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4113,6 +4273,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131009613</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4228,6 +4393,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115462916</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4343,6 +4513,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115462944</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4458,6 +4633,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115462910</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4560,6 +4740,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994546</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4662,6 +4847,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994542</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4764,6 +4954,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994411</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4866,6 +5061,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994539</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4968,6 +5168,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994541</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5070,6 +5275,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994543</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5172,6 +5382,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994544</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5274,6 +5489,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994412</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5376,6 +5596,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994540</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5478,6 +5703,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114994545</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5586,8 +5816,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108971706</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>